--- a/dados/Dados agregados/B4_dados_agregados.xlsx
+++ b/dados/Dados agregados/B4_dados_agregados.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Índice" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Índice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tab 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tab 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tab 3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tab 4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Tab 5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Tab 6" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -265,21 +265,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3415952"/>
+    <ext cx="5905500" cy="3331047"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -290,7 +290,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -298,21 +298,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3469613"/>
+    <ext cx="5905500" cy="3395274"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -331,21 +331,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="4564003"/>
+    <ext cx="5905500" cy="4393542"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -356,7 +356,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -364,21 +364,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3462849"/>
+    <ext cx="5905500" cy="3457444"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -389,7 +389,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -397,21 +397,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3447535"/>
+    <ext cx="5905500" cy="3377809"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -422,7 +422,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -430,21 +430,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3228593"/>
+    <ext cx="5905500" cy="2847805"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
